--- a/template.xlsx
+++ b/template.xlsx
@@ -5,29 +5,26 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3F11\Desktop\칼라매칭솔루션\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3F11\Desktop\TS_Colordata RD 통합\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84388097-E43A-4898-B501-3D7E285B8294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F51E52A-3622-4F96-AC7F-98FC9288563E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="446" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="975" windowWidth="15885" windowHeight="15225" tabRatio="446" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Reactive (3)" sheetId="19" r:id="rId1"/>
-    <sheet name="Reactive (2)" sheetId="18" r:id="rId2"/>
+    <sheet name="Reactive" sheetId="19" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Reactive (2)'!$A$1:$J$24</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Reactive (3)'!$A$1:$I$21</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Reactive (2)'!$A:$E,'Reactive (2)'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Reactive (3)'!$A:$E,'Reactive (3)'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Reactive!$A$1:$I$39</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Reactive!$A:$E,Reactive!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t xml:space="preserve">
 </t>
@@ -78,20 +75,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CMC DE*
-D65</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> Ohyoung's substrate : CM 40's Interlock</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>R1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>% o.w.f.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -123,64 +107,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> Ohyoung's substrate : Poly 100% 75/72 Interlock</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OHYOUNG / SangChul CHOI</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2021-01-79</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>January 28th, 2021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MI(1,3)
-A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Suncron Yellow Brown S-2RFL 150%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Suncron Red S-3BSN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Suncron Blue S-2G</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunfix Yellow SPD conc.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunfix Red SPD conc.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sunfix Navy Blue SB conc.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Color Name : Jet Gray 010 nOSC U01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MI(1,2)
-U35</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Color Name : </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -221,7 +147,7 @@
     <numFmt numFmtId="178" formatCode="0.0000_);[Red]\(0.0000\)"/>
     <numFmt numFmtId="179" formatCode="0.0000_ "/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="돋움"/>
@@ -297,34 +223,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="major"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -339,7 +244,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="35">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -352,26 +257,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -427,19 +312,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="22"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -461,30 +333,6 @@
       <left/>
       <right style="medium">
         <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="22"/>
-      </left>
-      <right style="medium">
-        <color theme="0" tint="-0.249977111117893"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="22"/>
-      </left>
-      <right style="medium">
-        <color theme="0" tint="-0.249977111117893"/>
       </right>
       <top/>
       <bottom style="medium">
@@ -583,125 +431,6 @@
     </border>
     <border>
       <left style="medium">
-        <color indexed="22"/>
-      </left>
-      <right style="medium">
-        <color indexed="22"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="22"/>
-      </left>
-      <right style="medium">
-        <color theme="0" tint="-0.249977111117893"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="0" tint="-0.249977111117893"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="0" tint="-0.249977111117893"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="0" tint="-0.249977111117893"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
         <color theme="0" tint="-0.249977111117893"/>
       </left>
       <right/>
@@ -743,7 +472,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -792,17 +521,8 @@
     <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -813,79 +533,49 @@
     <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -903,122 +593,38 @@
     <xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1216,160 +822,6 @@
           <a:headEnd type="none" w="med" len="med"/>
           <a:tailEnd type="none" w="med" len="med"/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>74257</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>189744</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>527382</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{588F2F55-100B-41FA-98E2-D578E85F72D5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0">
-          <a:picLocks noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="74257" y="845727"/>
-          <a:ext cx="1787673" cy="337638"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>31749</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>434837</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>96139</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{710594E2-AB1D-4024-BBDB-2A000FC98472}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0">
-          <a:picLocks noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="38100" y="31749"/>
-          <a:ext cx="7296150" cy="778765"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>115120</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>231913</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>619120</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>238957</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="그림 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82AEB7DD-3EA2-46DB-91DE-E677E0788C27}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:srcRect l="15790" r="15790"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="115120" y="4663109"/>
-          <a:ext cx="504000" cy="504000"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1678,10 +1130,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="56.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
+      <c r="B1" s="36"/>
       <c r="C1" s="10"/>
       <c r="E1" s="5"/>
       <c r="F1" s="5"/>
@@ -1690,7 +1142,7 @@
     </row>
     <row r="2" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="8"/>
-      <c r="B2" s="20"/>
+      <c r="B2" s="17"/>
       <c r="C2" s="10"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
@@ -1701,10 +1153,10 @@
       <c r="A3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="50" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="51"/>
+      <c r="B3" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="38"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -1714,20 +1166,20 @@
       <c r="A4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="51" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="51"/>
+      <c r="B4" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="38"/>
       <c r="D4" s="4"/>
     </row>
     <row r="5" spans="1:11" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="51" t="s">
+      <c r="B5" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="51"/>
+      <c r="C5" s="38"/>
       <c r="D5" s="4"/>
       <c r="H5" s="7"/>
     </row>
@@ -1735,141 +1187,141 @@
       <c r="A6" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="52">
+      <c r="B6" s="39">
         <v>46115</v>
       </c>
-      <c r="C6" s="52"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
     </row>
     <row r="7" spans="1:11" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="12" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C7" s="11"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="48" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
+      <c r="A8" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
       <c r="K8" s="9"/>
     </row>
     <row r="9" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="53" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
+      <c r="A9" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="40"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
     </row>
     <row r="10" spans="1:11" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="47"/>
+        <v>15</v>
+      </c>
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="34"/>
     </row>
     <row r="11" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="41" t="s">
+      <c r="D11" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="42"/>
-      <c r="I11" s="43"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="30"/>
     </row>
     <row r="12" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="44"/>
-      <c r="B12" s="62" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="58"/>
+      <c r="A12" s="31"/>
+      <c r="B12" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="45"/>
     </row>
     <row r="13" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="44"/>
-      <c r="B13" s="62"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="56"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="58"/>
+      <c r="A13" s="31"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="45"/>
     </row>
     <row r="14" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="44"/>
-      <c r="B14" s="62"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="56"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="58"/>
+      <c r="A14" s="31"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="45"/>
     </row>
     <row r="15" spans="1:11" ht="18.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="45"/>
-      <c r="B15" s="63"/>
-      <c r="C15" s="33" t="s">
+      <c r="A15" s="32"/>
+      <c r="B15" s="50"/>
+      <c r="C15" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="40">
+      <c r="D15" s="27">
         <f>SUM(D12:D14)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="61"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="48"/>
     </row>
     <row r="16" spans="1:11" ht="18.95" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="17" ht="18.95" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -1940,379 +1392,4 @@
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L24"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="12.75" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="9.109375" style="13" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="24.5546875" style="14" customWidth="1"/>
-    <col min="4" max="4" width="7.88671875" style="3" customWidth="1"/>
-    <col min="5" max="7" width="6.109375" style="6" customWidth="1"/>
-    <col min="8" max="8" width="7.33203125" style="6" customWidth="1"/>
-    <col min="9" max="9" width="6" style="6" customWidth="1"/>
-    <col min="10" max="10" width="6" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="56.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="49" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="10"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-    </row>
-    <row r="2" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="8"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="10"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-    </row>
-    <row r="3" spans="1:12" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="91" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="51"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-    </row>
-    <row r="4" spans="1:12" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="51" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="1:12" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="51"/>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:12" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="52" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="52"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-    </row>
-    <row r="7" spans="1:12" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-    </row>
-    <row r="8" spans="1:12" ht="51" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="48" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48"/>
-      <c r="L8" s="9"/>
-    </row>
-    <row r="9" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="90" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="90"/>
-      <c r="C9" s="90"/>
-      <c r="D9" s="90"/>
-      <c r="E9" s="90"/>
-      <c r="F9" s="90"/>
-      <c r="G9" s="90"/>
-      <c r="H9" s="90"/>
-      <c r="I9" s="90"/>
-      <c r="J9" s="90"/>
-    </row>
-    <row r="10" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="53" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
-    </row>
-    <row r="11" spans="1:12" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="17"/>
-    </row>
-    <row r="12" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="79" t="s">
-        <v>10</v>
-      </c>
-      <c r="I12" s="80"/>
-      <c r="J12" s="81"/>
-    </row>
-    <row r="13" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="82"/>
-      <c r="B13" s="62" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="19">
-        <v>0.94240000000000002</v>
-      </c>
-      <c r="E13" s="54">
-        <v>0.09</v>
-      </c>
-      <c r="F13" s="54">
-        <v>0.75</v>
-      </c>
-      <c r="G13" s="87">
-        <v>0.79</v>
-      </c>
-      <c r="H13" s="73"/>
-      <c r="I13" s="74"/>
-      <c r="J13" s="75"/>
-    </row>
-    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="83"/>
-      <c r="B14" s="62"/>
-      <c r="C14" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="19">
-        <v>0.51129999999999998</v>
-      </c>
-      <c r="E14" s="54"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="87"/>
-      <c r="H14" s="67"/>
-      <c r="I14" s="68"/>
-      <c r="J14" s="69"/>
-    </row>
-    <row r="15" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="83"/>
-      <c r="B15" s="62"/>
-      <c r="C15" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="19">
-        <v>1.1475</v>
-      </c>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="87"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="69"/>
-    </row>
-    <row r="16" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="83"/>
-      <c r="B16" s="85"/>
-      <c r="C16" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="31">
-        <f>SUM(D13:D15)</f>
-        <v>2.6012</v>
-      </c>
-      <c r="E16" s="86"/>
-      <c r="F16" s="86"/>
-      <c r="G16" s="88"/>
-      <c r="H16" s="76"/>
-      <c r="I16" s="77"/>
-      <c r="J16" s="78"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="83"/>
-      <c r="B17" s="62" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="19">
-        <v>1.0362</v>
-      </c>
-      <c r="E17" s="54">
-        <v>0.01</v>
-      </c>
-      <c r="F17" s="54">
-        <v>0.06</v>
-      </c>
-      <c r="G17" s="87">
-        <v>0.68</v>
-      </c>
-      <c r="H17" s="64"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="66"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="83"/>
-      <c r="B18" s="62"/>
-      <c r="C18" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="19">
-        <v>0.55420000000000003</v>
-      </c>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="87"/>
-      <c r="H18" s="67"/>
-      <c r="I18" s="68"/>
-      <c r="J18" s="69"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="83"/>
-      <c r="B19" s="62"/>
-      <c r="C19" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="19">
-        <v>1.3474999999999999</v>
-      </c>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="87"/>
-      <c r="H19" s="67"/>
-      <c r="I19" s="68"/>
-      <c r="J19" s="69"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="84"/>
-      <c r="B20" s="63"/>
-      <c r="C20" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="30">
-        <f>SUM(D17:D19)</f>
-        <v>2.9379</v>
-      </c>
-      <c r="E20" s="55"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="72"/>
-    </row>
-    <row r="21" spans="1:10" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="C21" s="28"/>
-    </row>
-    <row r="22" spans="1:10" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-    </row>
-    <row r="23" spans="1:10" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-    </row>
-    <row r="24" spans="1:10" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-    </row>
-  </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="H17:J20"/>
-    <mergeCell ref="H13:J16"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="A13:A20"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="E13:E16"/>
-    <mergeCell ref="G13:G16"/>
-    <mergeCell ref="F17:F20"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="E17:E20"/>
-    <mergeCell ref="G17:G20"/>
-    <mergeCell ref="F13:F16"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" fitToWidth="0" orientation="portrait" r:id="rId1"/>
-  <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;C &amp;P/&amp;N</oddFooter>
-  </headerFooter>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>